--- a/corrected-bank-specimens-for-user/06-bank-of-africa/parsed-excel/Excel Statement - COCOBOD CURRENT (1) - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/06-bank-of-africa/parsed-excel/Excel Statement - COCOBOD CURRENT (1) - parsed.xlsx
@@ -430,7 +430,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-08T16:17:01.184Z</v>
+        <v>2026-07-14T13:50:03.984Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/06-bank-of-africa/parsed-excel/Excel Statement - COCOBOD CURRENT (1) - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/06-bank-of-africa/parsed-excel/Excel Statement - COCOBOD CURRENT (1) - parsed.xlsx
@@ -430,7 +430,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-14T13:50:03.984Z</v>
+        <v>2026-07-17T19:29:57.753Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/06-bank-of-africa/parsed-excel/Excel Statement - COCOBOD CURRENT (1) - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/06-bank-of-africa/parsed-excel/Excel Statement - COCOBOD CURRENT (1) - parsed.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG26"/>
+  <dimension ref="A1:J26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,7 +430,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-17T19:29:57.753Z</v>
+        <v>2026-08-10T12:09:44.318Z</v>
       </c>
     </row>
     <row r="5">
@@ -477,96 +477,27 @@
         <v>Description</v>
       </c>
       <c r="G9" t="str">
-        <v>DEBIT</v>
+        <v>Debit</v>
       </c>
       <c r="H9" t="str">
-        <v>CREDIT</v>
+        <v>Credit</v>
       </c>
       <c r="I9" t="str">
-        <v>CHEQUE NUMBER</v>
+        <v>Cheque Number</v>
       </c>
       <c r="J9" t="str">
-        <v>BALANCE</v>
-      </c>
-      <c r="K9" t="str">
-        <v>control</v>
-      </c>
-      <c r="L9" t="str">
-        <v>Col_11</v>
-      </c>
-      <c r="M9" t="str">
-        <v>Col_12</v>
-      </c>
-      <c r="N9" t="str">
-        <v>Col_13</v>
-      </c>
-      <c r="O9" t="str">
-        <v>Col_14</v>
-      </c>
-      <c r="P9" t="str">
-        <v>Col_15</v>
-      </c>
-      <c r="Q9" t="str">
-        <v>Col_16</v>
-      </c>
-      <c r="R9" t="str">
-        <v>Col_17</v>
-      </c>
-      <c r="S9" t="str">
-        <v>Col_18</v>
-      </c>
-      <c r="T9" t="str">
-        <v>Col_19</v>
-      </c>
-      <c r="U9" t="str">
-        <v>Col_20</v>
-      </c>
-      <c r="V9" t="str">
-        <v>Col_21</v>
-      </c>
-      <c r="W9" t="str">
-        <v>Col_22</v>
-      </c>
-      <c r="X9" t="str">
-        <v>Col_23</v>
-      </c>
-      <c r="Y9" t="str">
-        <v>Col_24</v>
-      </c>
-      <c r="Z9" t="str">
-        <v>Col_25</v>
-      </c>
-      <c r="AA9" t="str">
-        <v>Col_26</v>
-      </c>
-      <c r="AB9" t="str">
-        <v>Col_27</v>
-      </c>
-      <c r="AC9" t="str">
-        <v>Col_28</v>
-      </c>
-      <c r="AD9" t="str">
-        <v>Col_29</v>
-      </c>
-      <c r="AE9" t="str">
-        <v>Col_30</v>
-      </c>
-      <c r="AF9" t="str">
-        <v>Col_31</v>
-      </c>
-      <c r="AG9" t="str">
-        <v>Col_32</v>
+        <v>Balance</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve"> AX21156 </v>
+        <v>AX21156</v>
       </c>
       <c r="B10" t="str">
         <v>DCI</v>
       </c>
       <c r="C10" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D10" t="str">
         <v>11-Sep-23</v>
@@ -577,34 +508,22 @@
       <c r="F10" t="str">
         <v>MAT.DEPOT</v>
       </c>
-      <c r="G10" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="H10" t="str">
-        <v xml:space="preserve"> 105,960.08 </v>
-      </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
-        <v xml:space="preserve"> 112,524.92 </v>
-      </c>
-      <c r="K10" t="str">
-        <v xml:space="preserve"> 1 </v>
-      </c>
-      <c r="M10" t="str">
-        <v>1</v>
+      <c r="H10">
+        <v>105960.08</v>
+      </c>
+      <c r="J10">
+        <v>112524.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve"> AX21156 </v>
+        <v>AX21156</v>
       </c>
       <c r="B11" t="str">
-        <v xml:space="preserve"> DCI </v>
+        <v>DCI</v>
       </c>
       <c r="C11" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D11" t="str">
         <v>11-Sep-23</v>
@@ -613,36 +532,24 @@
         <v>9-Sep-23</v>
       </c>
       <c r="F11" t="str">
-        <v xml:space="preserve"> MAT.DEPOT </v>
-      </c>
-      <c r="G11" t="str">
-        <v xml:space="preserve"> 106,169.10 </v>
-      </c>
-      <c r="H11" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
-        <v xml:space="preserve"> 6,355.82 </v>
-      </c>
-      <c r="K11" t="str">
-        <v xml:space="preserve"> 2 </v>
-      </c>
-      <c r="M11" t="str">
-        <v>2</v>
+        <v>MAT.DEPOT</v>
+      </c>
+      <c r="G11">
+        <v>106169.1</v>
+      </c>
+      <c r="J11">
+        <v>6355.82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve"> AX21156 </v>
+        <v>AX21156</v>
       </c>
       <c r="B12" t="str">
-        <v xml:space="preserve"> DCI </v>
+        <v>DCI</v>
       </c>
       <c r="C12" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D12" t="str">
         <v>11-Sep-23</v>
@@ -651,36 +558,24 @@
         <v>9-Sep-23</v>
       </c>
       <c r="F12" t="str">
-        <v xml:space="preserve"> MAT.DEPOT </v>
-      </c>
-      <c r="G12" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="H12" t="str">
-        <v xml:space="preserve"> 209.02 </v>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
-        <v xml:space="preserve"> 6,564.84 </v>
-      </c>
-      <c r="K12" t="str">
-        <v xml:space="preserve"> 3 </v>
-      </c>
-      <c r="M12" t="str">
-        <v>3</v>
+        <v>MAT.DEPOT</v>
+      </c>
+      <c r="H12">
+        <v>209.02</v>
+      </c>
+      <c r="J12">
+        <v>6564.84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve"> AX21514 </v>
+        <v>AX21514</v>
       </c>
       <c r="B13" t="str">
-        <v xml:space="preserve"> DCI </v>
+        <v>DCI</v>
       </c>
       <c r="C13" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D13" t="str">
         <v>11-Sep-23</v>
@@ -689,36 +584,24 @@
         <v>10-Sep-23</v>
       </c>
       <c r="F13" t="str">
-        <v xml:space="preserve"> MAT.DEPOT </v>
-      </c>
-      <c r="G13" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="H13" t="str">
-        <v xml:space="preserve"> 450.99 </v>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
-        <v xml:space="preserve"> 7,015.83 </v>
-      </c>
-      <c r="K13" t="str">
-        <v xml:space="preserve"> 4 </v>
-      </c>
-      <c r="M13" t="str">
-        <v>4</v>
+        <v>MAT.DEPOT</v>
+      </c>
+      <c r="H13">
+        <v>450.99</v>
+      </c>
+      <c r="J13">
+        <v>7015.83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v xml:space="preserve"> AX21514 </v>
+        <v>AX21514</v>
       </c>
       <c r="B14" t="str">
-        <v xml:space="preserve"> DCI </v>
+        <v>DCI</v>
       </c>
       <c r="C14" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D14" t="str">
         <v>11-Sep-23</v>
@@ -727,36 +610,24 @@
         <v>10-Sep-23</v>
       </c>
       <c r="F14" t="str">
-        <v xml:space="preserve"> MAT.DEPOT </v>
-      </c>
-      <c r="G14" t="str">
-        <v xml:space="preserve"> 137,628.57 </v>
-      </c>
-      <c r="H14" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-      <c r="J14" t="str">
-        <v xml:space="preserve"> (130,612.74)</v>
-      </c>
-      <c r="K14" t="str">
-        <v xml:space="preserve"> 5 </v>
-      </c>
-      <c r="M14" t="str">
-        <v>5</v>
+        <v>MAT.DEPOT</v>
+      </c>
+      <c r="G14">
+        <v>137628.57</v>
+      </c>
+      <c r="J14">
+        <v>-130612.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve"> AX21514 </v>
+        <v>AX21514</v>
       </c>
       <c r="B15" t="str">
-        <v xml:space="preserve"> DCI </v>
+        <v>DCI</v>
       </c>
       <c r="C15" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D15" t="str">
         <v>11-Sep-23</v>
@@ -765,36 +636,24 @@
         <v>10-Sep-23</v>
       </c>
       <c r="F15" t="str">
-        <v xml:space="preserve"> MAT.DEPOT </v>
-      </c>
-      <c r="G15" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="H15" t="str">
-        <v xml:space="preserve"> 137,177.58 </v>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v xml:space="preserve"> 6,564.84 </v>
-      </c>
-      <c r="K15" t="str">
-        <v xml:space="preserve"> 6 </v>
-      </c>
-      <c r="M15" t="str">
-        <v>6</v>
+        <v>MAT.DEPOT</v>
+      </c>
+      <c r="H15">
+        <v>137177.58</v>
+      </c>
+      <c r="J15">
+        <v>6564.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve"> AX21528 </v>
+        <v>AX21528</v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve"> DCI </v>
+        <v>DCI</v>
       </c>
       <c r="C16" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D16" t="str">
         <v>11-Sep-23</v>
@@ -803,36 +662,24 @@
         <v>10-Sep-23</v>
       </c>
       <c r="F16" t="str">
-        <v xml:space="preserve"> MAT.DEPOT </v>
-      </c>
-      <c r="G16" t="str">
-        <v xml:space="preserve"> 142,123.62 </v>
-      </c>
-      <c r="H16" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
-        <v xml:space="preserve"> (135,558.78)</v>
-      </c>
-      <c r="K16" t="str">
-        <v xml:space="preserve"> 7 </v>
-      </c>
-      <c r="M16" t="str">
-        <v>7</v>
+        <v>MAT.DEPOT</v>
+      </c>
+      <c r="G16">
+        <v>142123.62</v>
+      </c>
+      <c r="J16">
+        <v>-135558.78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve"> AX21528 </v>
+        <v>AX21528</v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> DCI </v>
+        <v>DCI</v>
       </c>
       <c r="C17" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D17" t="str">
         <v>11-Sep-23</v>
@@ -841,36 +688,24 @@
         <v>10-Sep-23</v>
       </c>
       <c r="F17" t="str">
-        <v xml:space="preserve"> MAT.DEPOT </v>
-      </c>
-      <c r="G17" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="H17" t="str">
-        <v xml:space="preserve"> 141,657.90 </v>
-      </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
-        <v xml:space="preserve"> 6,099.12 </v>
-      </c>
-      <c r="K17" t="str">
-        <v xml:space="preserve"> 8 </v>
-      </c>
-      <c r="M17" t="str">
-        <v>8</v>
+        <v>MAT.DEPOT</v>
+      </c>
+      <c r="H17">
+        <v>141657.9</v>
+      </c>
+      <c r="J17">
+        <v>6099.12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve"> AX21528 </v>
+        <v>AX21528</v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve"> DCI </v>
+        <v>DCI</v>
       </c>
       <c r="C18" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D18" t="str">
         <v>11-Sep-23</v>
@@ -879,36 +714,24 @@
         <v>10-Sep-23</v>
       </c>
       <c r="F18" t="str">
-        <v xml:space="preserve"> MAT.DEPOT </v>
-      </c>
-      <c r="G18" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="H18" t="str">
-        <v xml:space="preserve"> 465.72 </v>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v xml:space="preserve"> 6,564.84 </v>
-      </c>
-      <c r="K18" t="str">
-        <v xml:space="preserve"> 9 </v>
-      </c>
-      <c r="M18" t="str">
-        <v>9</v>
+        <v>MAT.DEPOT</v>
+      </c>
+      <c r="H18">
+        <v>465.72</v>
+      </c>
+      <c r="J18">
+        <v>6564.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve"> 2300464 </v>
+        <v>2300464</v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve"> CHQRE </v>
+        <v>CHQRE</v>
       </c>
       <c r="C19" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D19" t="str">
         <v>13-Sep-23</v>
@@ -917,36 +740,27 @@
         <v>13-Sep-23</v>
       </c>
       <c r="F19" t="str">
-        <v xml:space="preserve"> CHECK PAID  Cheque: 0000510 /BANK-34 /INW.CHQ /00000000 0000510 </v>
-      </c>
-      <c r="G19" t="str">
-        <v xml:space="preserve"> 5,514.07 </v>
-      </c>
-      <c r="H19" t="str">
-        <v xml:space="preserve"> -   </v>
+        <v>CHECK PAID Cheque: 0000510 /BANK-34 /INW.CHQ /00000000 0000510</v>
+      </c>
+      <c r="G19">
+        <v>5514.07</v>
       </c>
       <c r="I19" t="str">
-        <v xml:space="preserve">  0000510 </v>
-      </c>
-      <c r="J19" t="str">
-        <v xml:space="preserve"> 1,050.77 </v>
-      </c>
-      <c r="K19" t="str">
-        <v xml:space="preserve"> 10 </v>
-      </c>
-      <c r="M19" t="str">
-        <v>10</v>
+        <v>0000510</v>
+      </c>
+      <c r="J19">
+        <v>1050.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve"> 2300464 </v>
+        <v>2300464</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve"> CHQRE </v>
+        <v>CHQRE</v>
       </c>
       <c r="C20" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D20" t="str">
         <v>13-Sep-23</v>
@@ -955,36 +769,27 @@
         <v>13-Sep-23</v>
       </c>
       <c r="F20" t="str">
-        <v xml:space="preserve"> CHECK PAID  Cheque: 0000511 /BANK-34 /INW.CHQ /00000000 0000511 </v>
-      </c>
-      <c r="G20" t="str">
-        <v xml:space="preserve"> 2,968.26 </v>
-      </c>
-      <c r="H20" t="str">
-        <v xml:space="preserve"> -   </v>
+        <v>CHECK PAID Cheque: 0000511 /BANK-34 /INW.CHQ /00000000 0000511</v>
+      </c>
+      <c r="G20">
+        <v>2968.26</v>
       </c>
       <c r="I20" t="str">
-        <v xml:space="preserve">  0000511 </v>
-      </c>
-      <c r="J20" t="str">
-        <v xml:space="preserve"> (1,917.49)</v>
-      </c>
-      <c r="K20" t="str">
-        <v xml:space="preserve"> 11 </v>
-      </c>
-      <c r="M20" t="str">
-        <v>11</v>
+        <v>0000511</v>
+      </c>
+      <c r="J20">
+        <v>-1917.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve"> AX44672 </v>
+        <v>AX44672</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve"> DCR </v>
+        <v>DCR</v>
       </c>
       <c r="C21" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D21" t="str">
         <v>13-Sep-23</v>
@@ -993,36 +798,24 @@
         <v>13-Sep-23</v>
       </c>
       <c r="F21" t="str">
-        <v xml:space="preserve"> DECREASE RENEWAL DEPOSIT </v>
-      </c>
-      <c r="G21" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="H21" t="str">
-        <v xml:space="preserve"> 1,953.46 </v>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
-        <v xml:space="preserve"> 35.97 </v>
-      </c>
-      <c r="K21" t="str">
-        <v xml:space="preserve"> 12 </v>
-      </c>
-      <c r="M21" t="str">
-        <v>12</v>
+        <v>DECREASE RENEWAL DEPOSIT</v>
+      </c>
+      <c r="H21">
+        <v>1953.46</v>
+      </c>
+      <c r="J21">
+        <v>35.97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v xml:space="preserve"> AX44672 </v>
+        <v>AX44672</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve"> DCR </v>
+        <v>DCR</v>
       </c>
       <c r="C22" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D22" t="str">
         <v>13-Sep-23</v>
@@ -1031,36 +824,24 @@
         <v>13-Sep-23</v>
       </c>
       <c r="F22" t="str">
-        <v xml:space="preserve"> INT.DEPO 00291410301 GHANA COCOA BOARD COCO HOUSE </v>
-      </c>
-      <c r="G22" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="H22" t="str">
-        <v xml:space="preserve"> 46.54 </v>
-      </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <v xml:space="preserve"> 82.51 </v>
-      </c>
-      <c r="K22" t="str">
-        <v xml:space="preserve"> 13 </v>
-      </c>
-      <c r="M22" t="str">
-        <v>13</v>
+        <v>INT.DEPO 00291410301 GHANA COCOA BOARD COCO HOUSE</v>
+      </c>
+      <c r="H22">
+        <v>46.54</v>
+      </c>
+      <c r="J22">
+        <v>82.51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve"> 2301298 </v>
+        <v>2301298</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve"> CHQRE </v>
+        <v>CHQRE</v>
       </c>
       <c r="C23" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D23" t="str">
         <v>18-Sep-23</v>
@@ -1069,36 +850,27 @@
         <v>18-Sep-23</v>
       </c>
       <c r="F23" t="str">
-        <v xml:space="preserve"> CHECK PAID  Cheque: 0000505 /BANK-04 /INW.CHQ /00000000 0000505 </v>
-      </c>
-      <c r="G23" t="str">
-        <v xml:space="preserve"> 962.74 </v>
-      </c>
-      <c r="H23" t="str">
-        <v xml:space="preserve"> -   </v>
+        <v>CHECK PAID Cheque: 0000505 /BANK-04 /INW.CHQ /00000000 0000505</v>
+      </c>
+      <c r="G23">
+        <v>962.74</v>
       </c>
       <c r="I23" t="str">
-        <v xml:space="preserve">  0000505 </v>
-      </c>
-      <c r="J23" t="str">
-        <v xml:space="preserve"> (880.23)</v>
-      </c>
-      <c r="K23" t="str">
-        <v xml:space="preserve"> 14 </v>
-      </c>
-      <c r="M23" t="str">
-        <v>14</v>
+        <v>0000505</v>
+      </c>
+      <c r="J23">
+        <v>-880.23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve"> AX87761 </v>
+        <v>AX87761</v>
       </c>
       <c r="B24" t="str">
-        <v xml:space="preserve"> DCR </v>
+        <v>DCR</v>
       </c>
       <c r="C24" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D24" t="str">
         <v>18-Sep-23</v>
@@ -1107,36 +879,24 @@
         <v>18-Sep-23</v>
       </c>
       <c r="F24" t="str">
-        <v xml:space="preserve"> INT.DEPO 00291410301 GHANA COCOA BOARD COCO HOUSE </v>
-      </c>
-      <c r="G24" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="H24" t="str">
-        <v xml:space="preserve"> 57.10 </v>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v xml:space="preserve"> (823.13)</v>
-      </c>
-      <c r="K24" t="str">
-        <v xml:space="preserve"> 15 </v>
-      </c>
-      <c r="M24" t="str">
-        <v>15</v>
+        <v>INT.DEPO 00291410301 GHANA COCOA BOARD COCO HOUSE</v>
+      </c>
+      <c r="H24">
+        <v>57.1</v>
+      </c>
+      <c r="J24">
+        <v>-823.13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve"> AX87761 </v>
+        <v>AX87761</v>
       </c>
       <c r="B25" t="str">
-        <v xml:space="preserve"> DCR </v>
+        <v>DCR</v>
       </c>
       <c r="C25" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D25" t="str">
         <v>18-Sep-23</v>
@@ -1145,36 +905,24 @@
         <v>18-Sep-23</v>
       </c>
       <c r="F25" t="str">
-        <v xml:space="preserve"> DECREASE RENEWAL DEPOSIT </v>
-      </c>
-      <c r="G25" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="H25" t="str">
-        <v xml:space="preserve"> 14,942.90 </v>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v xml:space="preserve"> 14,119.77 </v>
-      </c>
-      <c r="K25" t="str">
-        <v xml:space="preserve"> 16 </v>
-      </c>
-      <c r="M25" t="str">
-        <v>16</v>
+        <v>DECREASE RENEWAL DEPOSIT</v>
+      </c>
+      <c r="H25">
+        <v>14942.9</v>
+      </c>
+      <c r="J25">
+        <v>14119.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve"> AX88098 </v>
+        <v>AX88098</v>
       </c>
       <c r="B26" t="str">
-        <v xml:space="preserve"> VE </v>
+        <v>VE</v>
       </c>
       <c r="C26" t="str">
-        <v xml:space="preserve"> 00291410102 </v>
+        <v>00291410102</v>
       </c>
       <c r="D26" t="str">
         <v>18-Sep-23</v>
@@ -1183,30 +931,18 @@
         <v>18-Sep-23</v>
       </c>
       <c r="F26" t="str">
-        <v xml:space="preserve"> YOUR CASH DEPOSIT ADELAIDE AGYEMANG </v>
-      </c>
-      <c r="G26" t="str">
-        <v xml:space="preserve"> -   </v>
-      </c>
-      <c r="H26" t="str">
-        <v xml:space="preserve"> 3,119.00 </v>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v xml:space="preserve"> 17,238.77 </v>
-      </c>
-      <c r="K26" t="str">
-        <v xml:space="preserve"> 17 </v>
-      </c>
-      <c r="M26" t="str">
-        <v>17</v>
+        <v>YOUR CASH DEPOSIT ADELAIDE AGYEMANG</v>
+      </c>
+      <c r="H26">
+        <v>3119</v>
+      </c>
+      <c r="J26">
+        <v>17238.77</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AG26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J26"/>
   </ignoredErrors>
 </worksheet>
 </file>